--- a/r4-core-main/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10706" uniqueCount="1033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10782" uniqueCount="1039">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:58:59+00:00</t>
+    <t>2026-10-19T05:20:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2143,10 +2143,26 @@
 </t>
   </si>
   <si>
-    <t>Address Municipality Code</t>
-  </si>
-  <si>
-    <t>HL7® Austria FHIR® Core Extension for the municipality code part of the Austrian address</t>
+    <t>Address Municipality Code (Gemeindecode)</t>
+  </si>
+  <si>
+    <t>HL7® Austria FHIR® Core Extension for the municipality code (Gemeindecode) part of the Austrian address. The municipality code is related to the [municipality key (Gemeindekennziffer)](https://fhir.hl7.at/core/r4/StructureDefinition-at-core-ext-address-municipalityKey.html). While these two are generally identical, there is one notable exception: in Vienna, the municipality key (Gemeindekennziffer) is consistently 90001, whereas the municipality code (Gemeindecode) varies by district. The current list of values is provided by [Statistik Austria](https://www.statistik.at/verzeichnis/reglisten/gemliste_knz.pdf).</t>
+  </si>
+  <si>
+    <t>Patient.address.extension:municipalityKey</t>
+  </si>
+  <si>
+    <t>municipalityKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-municipalityKey}
+</t>
+  </si>
+  <si>
+    <t>Address Municipality Key (Gemeindekennziffer)</t>
+  </si>
+  <si>
+    <t>HL7® Austria FHIR® Core Extension for the municipality key (Gemeindekennziffer) part of the Austrian address. The municipality key is related to the [municipality code (Gemeindecode)](https://fhir.hl7.at/core/r4/StructureDefinition-at-core-ext-address-municipalityCode.html). While these two are generally identical, there is one notable exception: in Vienna, the municipality key (Gemeindekennziffer) is consistently 90001, whereas the municipality code (Gemeindecode) varies by district. The current list of values is provided by [Statistik Austria](https://www.statistik.at/verzeichnis/reglisten/gemliste_knz.pdf).</t>
   </si>
   <si>
     <t>Patient.address.use</t>
@@ -2864,6 +2880,9 @@
   </si>
   <si>
     <t>Patient.contact.address.extension:municipalityCode</t>
+  </si>
+  <si>
+    <t>Patient.contact.address.extension:municipalityKey</t>
   </si>
   <si>
     <t>Patient.contact.address.use</t>
@@ -3505,7 +3524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP281"/>
+  <dimension ref="A1:AP283"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.27734375" customWidth="true" bestFit="true"/>
@@ -24184,9 +24203,11 @@
         <v>693</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="C173" s="2"/>
+        <v>687</v>
+      </c>
+      <c r="C173" t="s" s="2">
+        <v>694</v>
+      </c>
       <c r="D173" t="s" s="2">
         <v>21</v>
       </c>
@@ -24201,26 +24222,22 @@
         <v>21</v>
       </c>
       <c r="I173" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>110</v>
+        <v>695</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="O173" t="s" s="2">
         <v>697</v>
       </c>
+      <c r="N173" s="2"/>
+      <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>21</v>
       </c>
@@ -24232,7 +24249,7 @@
         <v>21</v>
       </c>
       <c r="T173" t="s" s="2">
-        <v>698</v>
+        <v>21</v>
       </c>
       <c r="U173" t="s" s="2">
         <v>21</v>
@@ -24244,13 +24261,13 @@
         <v>21</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>699</v>
+        <v>21</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>700</v>
+        <v>21</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>21</v>
@@ -24268,25 +24285,25 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>701</v>
+        <v>162</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI173" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>702</v>
+        <v>21</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>517</v>
+        <v>21</v>
       </c>
       <c r="AM173" t="s" s="2">
         <v>21</v>
@@ -24295,7 +24312,7 @@
         <v>21</v>
       </c>
       <c r="AO173" t="s" s="2">
-        <v>703</v>
+        <v>21</v>
       </c>
       <c r="AP173" t="s" s="2">
         <v>21</v>
@@ -24303,10 +24320,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -24323,7 +24340,7 @@
         <v>21</v>
       </c>
       <c r="I174" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J174" t="s" s="2">
         <v>91</v>
@@ -24332,15 +24349,17 @@
         <v>110</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="O174" s="2"/>
+        <v>701</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>702</v>
+      </c>
       <c r="P174" t="s" s="2">
         <v>21</v>
       </c>
@@ -24352,7 +24371,7 @@
         <v>21</v>
       </c>
       <c r="T174" t="s" s="2">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="U174" t="s" s="2">
         <v>21</v>
@@ -24367,10 +24386,10 @@
         <v>245</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>21</v>
@@ -24388,7 +24407,7 @@
         <v>21</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -24403,7 +24422,7 @@
         <v>102</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>21</v>
+        <v>707</v>
       </c>
       <c r="AL174" t="s" s="2">
         <v>517</v>
@@ -24415,7 +24434,7 @@
         <v>21</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="AP174" t="s" s="2">
         <v>21</v>
@@ -24423,10 +24442,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24449,20 +24468,18 @@
         <v>91</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>523</v>
-      </c>
+        <v>712</v>
+      </c>
+      <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>21</v>
       </c>
@@ -24474,7 +24491,7 @@
         <v>21</v>
       </c>
       <c r="T175" t="s" s="2">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="U175" t="s" s="2">
         <v>21</v>
@@ -24486,13 +24503,13 @@
         <v>21</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>21</v>
+        <v>714</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>21</v>
+        <v>715</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>21</v>
@@ -24510,7 +24527,7 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -24525,10 +24542,10 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>719</v>
+        <v>21</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>21</v>
@@ -24537,7 +24554,7 @@
         <v>21</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AP175" t="s" s="2">
         <v>21</v>
@@ -24545,10 +24562,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24559,7 +24576,7 @@
         <v>81</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>21</v>
@@ -24574,13 +24591,17 @@
         <v>150</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="N176" s="2"/>
-      <c r="O176" s="2"/>
+        <v>720</v>
+      </c>
+      <c r="N176" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="O176" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P176" t="s" s="2">
         <v>21</v>
       </c>
@@ -24592,7 +24613,7 @@
         <v>21</v>
       </c>
       <c r="T176" t="s" s="2">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="U176" t="s" s="2">
         <v>21</v>
@@ -24628,13 +24649,13 @@
         <v>21</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>21</v>
@@ -24643,10 +24664,10 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>727</v>
+        <v>525</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>21</v>
@@ -24655,7 +24676,7 @@
         <v>21</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="AP176" t="s" s="2">
         <v>21</v>
@@ -24663,10 +24684,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24677,7 +24698,7 @@
         <v>81</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>21</v>
@@ -24686,16 +24707,16 @@
         <v>21</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K177" t="s" s="2">
         <v>150</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>627</v>
+        <v>727</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>628</v>
+        <v>728</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -24710,7 +24731,7 @@
         <v>21</v>
       </c>
       <c r="T177" t="s" s="2">
-        <v>21</v>
+        <v>729</v>
       </c>
       <c r="U177" t="s" s="2">
         <v>21</v>
@@ -24746,25 +24767,25 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>153</v>
+        <v>730</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>21</v>
+        <v>731</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>21</v>
+        <v>732</v>
       </c>
       <c r="AM177" t="s" s="2">
         <v>21</v>
@@ -24773,7 +24794,7 @@
         <v>21</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>21</v>
+        <v>733</v>
       </c>
       <c r="AP177" t="s" s="2">
         <v>21</v>
@@ -24781,10 +24802,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24795,7 +24816,7 @@
         <v>81</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>21</v>
@@ -24807,13 +24828,13 @@
         <v>21</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>136</v>
+        <v>627</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>137</v>
+        <v>628</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -24852,29 +24873,31 @@
         <v>21</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC178" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD178" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>21</v>
@@ -24897,14 +24920,12 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>732</v>
-      </c>
+        <v>735</v>
+      </c>
+      <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
         <v>21</v>
       </c>
@@ -24913,7 +24934,7 @@
         <v>81</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>21</v>
@@ -24925,13 +24946,13 @@
         <v>21</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>733</v>
+        <v>135</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>734</v>
+        <v>136</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>735</v>
+        <v>137</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -24970,16 +24991,14 @@
         <v>21</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC179" s="2"/>
       <c r="AD179" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF179" t="s" s="2">
         <v>162</v>
@@ -24991,7 +25010,7 @@
         <v>82</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>141</v>
@@ -25000,7 +25019,7 @@
         <v>21</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>736</v>
+        <v>21</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>21</v>
@@ -25017,13 +25036,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C180" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C180" t="s" s="2">
-        <v>738</v>
       </c>
       <c r="D180" t="s" s="2">
         <v>21</v>
@@ -25045,13 +25064,13 @@
         <v>21</v>
       </c>
       <c r="K180" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="L180" t="s" s="2">
         <v>739</v>
       </c>
-      <c r="L180" t="s" s="2">
+      <c r="M180" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -25120,7 +25139,7 @@
         <v>21</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>21</v>
@@ -25137,13 +25156,13 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="C181" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C181" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="D181" t="s" s="2">
         <v>21</v>
@@ -25165,10 +25184,10 @@
         <v>21</v>
       </c>
       <c r="K181" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="L181" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="L181" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="M181" t="s" s="2">
         <v>746</v>
@@ -25260,7 +25279,7 @@
         <v>748</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="C182" t="s" s="2">
         <v>749</v>
@@ -25291,7 +25310,7 @@
         <v>751</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -25360,7 +25379,7 @@
         <v>21</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>21</v>
+        <v>752</v>
       </c>
       <c r="AM182" t="s" s="2">
         <v>21</v>
@@ -25380,9 +25399,11 @@
         <v>753</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="C183" s="2"/>
+        <v>735</v>
+      </c>
+      <c r="C183" t="s" s="2">
+        <v>754</v>
+      </c>
       <c r="D183" t="s" s="2">
         <v>21</v>
       </c>
@@ -25403,13 +25424,13 @@
         <v>21</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>150</v>
+        <v>755</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>659</v>
+        <v>757</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -25433,7 +25454,7 @@
         <v>21</v>
       </c>
       <c r="W183" t="s" s="2">
-        <v>755</v>
+        <v>21</v>
       </c>
       <c r="X183" t="s" s="2">
         <v>21</v>
@@ -25460,19 +25481,19 @@
         <v>21</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>637</v>
+        <v>162</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>21</v>
@@ -25495,14 +25516,14 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
-        <v>757</v>
+        <v>21</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
@@ -25518,16 +25539,16 @@
         <v>21</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K184" t="s" s="2">
         <v>150</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>759</v>
+        <v>659</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -25542,17 +25563,17 @@
         <v>21</v>
       </c>
       <c r="T184" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U184" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V184" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W184" t="s" s="2">
         <v>760</v>
       </c>
-      <c r="U184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W184" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="X184" t="s" s="2">
         <v>21</v>
       </c>
@@ -25578,7 +25599,7 @@
         <v>21</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>761</v>
+        <v>637</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
@@ -25590,13 +25611,13 @@
         <v>21</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>762</v>
+        <v>21</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>763</v>
+        <v>21</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>21</v>
@@ -25605,7 +25626,7 @@
         <v>21</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>764</v>
+        <v>21</v>
       </c>
       <c r="AP184" t="s" s="2">
         <v>21</v>
@@ -25613,21 +25634,21 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G185" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H185" t="s" s="2">
         <v>21</v>
@@ -25642,14 +25663,12 @@
         <v>150</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>769</v>
-      </c>
+        <v>764</v>
+      </c>
+      <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
         <v>21</v>
@@ -25662,7 +25681,7 @@
         <v>21</v>
       </c>
       <c r="T185" t="s" s="2">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="U185" t="s" s="2">
         <v>21</v>
@@ -25698,7 +25717,7 @@
         <v>21</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -25713,10 +25732,10 @@
         <v>102</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>21</v>
+        <v>767</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="AM185" t="s" s="2">
         <v>21</v>
@@ -25725,7 +25744,7 @@
         <v>21</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="AP185" t="s" s="2">
         <v>21</v>
@@ -25733,21 +25752,21 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>21</v>
@@ -25762,12 +25781,14 @@
         <v>150</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="N186" s="2"/>
+        <v>773</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>774</v>
+      </c>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
         <v>21</v>
@@ -25780,7 +25801,7 @@
         <v>21</v>
       </c>
       <c r="T186" t="s" s="2">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="U186" t="s" s="2">
         <v>21</v>
@@ -25816,7 +25837,7 @@
         <v>21</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>81</v>
@@ -25831,10 +25852,10 @@
         <v>102</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>779</v>
+        <v>21</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>21</v>
@@ -25843,7 +25864,7 @@
         <v>21</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="AP186" t="s" s="2">
         <v>21</v>
@@ -25851,14 +25872,14 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
@@ -25880,10 +25901,10 @@
         <v>150</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="N187" s="2"/>
       <c r="O187" s="2"/>
@@ -25898,7 +25919,7 @@
         <v>21</v>
       </c>
       <c r="T187" t="s" s="2">
-        <v>786</v>
+        <v>21</v>
       </c>
       <c r="U187" t="s" s="2">
         <v>21</v>
@@ -25934,7 +25955,7 @@
         <v>21</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -25949,10 +25970,10 @@
         <v>102</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>21</v>
@@ -25961,7 +25982,7 @@
         <v>21</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="AP187" t="s" s="2">
         <v>21</v>
@@ -25969,14 +25990,14 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
-        <v>21</v>
+        <v>788</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
@@ -25998,14 +26019,12 @@
         <v>150</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>794</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="N188" s="2"/>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
         <v>21</v>
@@ -26018,7 +26037,7 @@
         <v>21</v>
       </c>
       <c r="T188" t="s" s="2">
-        <v>21</v>
+        <v>791</v>
       </c>
       <c r="U188" t="s" s="2">
         <v>21</v>
@@ -26054,7 +26073,7 @@
         <v>21</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -26069,10 +26088,10 @@
         <v>102</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>21</v>
@@ -26081,7 +26100,7 @@
         <v>21</v>
       </c>
       <c r="AO188" t="s" s="2">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="AP188" t="s" s="2">
         <v>21</v>
@@ -26089,10 +26108,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -26103,7 +26122,7 @@
         <v>81</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H189" t="s" s="2">
         <v>21</v>
@@ -26115,18 +26134,18 @@
         <v>91</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="N189" s="2"/>
-      <c r="O189" t="s" s="2">
-        <v>802</v>
-      </c>
+        <v>798</v>
+      </c>
+      <c r="N189" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
         <v>21</v>
       </c>
@@ -26138,7 +26157,7 @@
         <v>21</v>
       </c>
       <c r="T189" t="s" s="2">
-        <v>803</v>
+        <v>21</v>
       </c>
       <c r="U189" t="s" s="2">
         <v>21</v>
@@ -26174,7 +26193,7 @@
         <v>21</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
@@ -26189,10 +26208,10 @@
         <v>102</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>21</v>
+        <v>801</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>564</v>
+        <v>802</v>
       </c>
       <c r="AM189" t="s" s="2">
         <v>21</v>
@@ -26201,7 +26220,7 @@
         <v>21</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="AP189" t="s" s="2">
         <v>21</v>
@@ -26209,10 +26228,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -26223,7 +26242,7 @@
         <v>81</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H190" t="s" s="2">
         <v>21</v>
@@ -26232,20 +26251,20 @@
         <v>21</v>
       </c>
       <c r="J190" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" t="s" s="2">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>21</v>
@@ -26258,7 +26277,7 @@
         <v>21</v>
       </c>
       <c r="T190" t="s" s="2">
-        <v>21</v>
+        <v>808</v>
       </c>
       <c r="U190" t="s" s="2">
         <v>21</v>
@@ -26270,13 +26289,13 @@
         <v>21</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="Y190" t="s" s="2">
-        <v>810</v>
+        <v>21</v>
       </c>
       <c r="Z190" t="s" s="2">
-        <v>811</v>
+        <v>21</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>21</v>
@@ -26294,7 +26313,7 @@
         <v>21</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>81</v>
@@ -26312,16 +26331,16 @@
         <v>21</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>812</v>
+        <v>564</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>813</v>
+        <v>21</v>
       </c>
       <c r="AN190" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO190" t="s" s="2">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="AP190" t="s" s="2">
         <v>21</v>
@@ -26329,10 +26348,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -26355,16 +26374,18 @@
         <v>21</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>151</v>
+        <v>812</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>152</v>
+        <v>813</v>
       </c>
       <c r="N191" s="2"/>
-      <c r="O191" s="2"/>
+      <c r="O191" t="s" s="2">
+        <v>814</v>
+      </c>
       <c r="P191" t="s" s="2">
         <v>21</v>
       </c>
@@ -26388,13 +26409,13 @@
         <v>21</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="Y191" t="s" s="2">
-        <v>21</v>
+        <v>815</v>
       </c>
       <c r="Z191" t="s" s="2">
-        <v>21</v>
+        <v>816</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>21</v>
@@ -26412,7 +26433,7 @@
         <v>21</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>153</v>
+        <v>811</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
@@ -26424,22 +26445,22 @@
         <v>21</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK191" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>154</v>
+        <v>817</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>21</v>
+        <v>818</v>
       </c>
       <c r="AN191" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>21</v>
+        <v>819</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>21</v>
@@ -26447,21 +26468,21 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>21</v>
@@ -26473,17 +26494,15 @@
         <v>21</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>21</v>
@@ -26520,31 +26539,31 @@
         <v>21</v>
       </c>
       <c r="AB192" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC192" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AD192" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE192" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI192" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>21</v>
@@ -26567,14 +26586,14 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
@@ -26590,23 +26609,21 @@
         <v>21</v>
       </c>
       <c r="J193" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>301</v>
+        <v>135</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>302</v>
+        <v>158</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>303</v>
+        <v>159</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O193" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
         <v>21</v>
       </c>
@@ -26642,19 +26659,19 @@
         <v>21</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>306</v>
+        <v>162</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -26666,13 +26683,13 @@
         <v>21</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>307</v>
+        <v>154</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>21</v>
@@ -26681,7 +26698,7 @@
         <v>21</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="AP193" t="s" s="2">
         <v>21</v>
@@ -26689,10 +26706,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26703,7 +26720,7 @@
         <v>81</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>21</v>
@@ -26712,19 +26729,23 @@
         <v>21</v>
       </c>
       <c r="J194" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>151</v>
+        <v>302</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N194" s="2"/>
-      <c r="O194" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P194" t="s" s="2">
         <v>21</v>
       </c>
@@ -26772,25 +26793,25 @@
         <v>21</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>153</v>
+        <v>306</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI194" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK194" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>154</v>
+        <v>307</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>21</v>
@@ -26799,7 +26820,7 @@
         <v>21</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
       <c r="AP194" t="s" s="2">
         <v>21</v>
@@ -26807,21 +26828,21 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>21</v>
@@ -26833,17 +26854,15 @@
         <v>21</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N195" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N195" s="2"/>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
         <v>21</v>
@@ -26880,31 +26899,31 @@
         <v>21</v>
       </c>
       <c r="AB195" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC195" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AD195" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE195" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI195" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK195" t="s" s="2">
         <v>21</v>
@@ -26927,21 +26946,21 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>21</v>
@@ -26950,23 +26969,21 @@
         <v>21</v>
       </c>
       <c r="J196" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>315</v>
+        <v>158</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>316</v>
+        <v>159</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
         <v>21</v>
       </c>
@@ -27002,37 +27019,37 @@
         <v>21</v>
       </c>
       <c r="AB196" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC196" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AD196" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE196" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>320</v>
+        <v>162</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>821</v>
+        <v>21</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>321</v>
+        <v>154</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>21</v>
@@ -27041,7 +27058,7 @@
         <v>21</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="AP196" t="s" s="2">
         <v>21</v>
@@ -27049,10 +27066,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -27075,18 +27092,20 @@
         <v>91</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O197" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="O197" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P197" t="s" s="2">
         <v>21</v>
       </c>
@@ -27134,7 +27153,7 @@
         <v>21</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>81</v>
@@ -27149,10 +27168,10 @@
         <v>102</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>21</v>
+        <v>826</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="AM197" t="s" s="2">
         <v>21</v>
@@ -27161,7 +27180,7 @@
         <v>21</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="AP197" t="s" s="2">
         <v>21</v>
@@ -27169,10 +27188,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -27195,18 +27214,18 @@
         <v>91</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N198" s="2"/>
-      <c r="O198" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N198" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
         <v>21</v>
       </c>
@@ -27254,7 +27273,7 @@
         <v>21</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
@@ -27269,10 +27288,10 @@
         <v>102</v>
       </c>
       <c r="AK198" t="s" s="2">
-        <v>824</v>
+        <v>21</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AM198" t="s" s="2">
         <v>21</v>
@@ -27281,7 +27300,7 @@
         <v>21</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="AP198" t="s" s="2">
         <v>21</v>
@@ -27289,10 +27308,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -27315,17 +27334,17 @@
         <v>91</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>21</v>
@@ -27374,7 +27393,7 @@
         <v>21</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -27389,10 +27408,10 @@
         <v>102</v>
       </c>
       <c r="AK199" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AM199" t="s" s="2">
         <v>21</v>
@@ -27401,7 +27420,7 @@
         <v>21</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AP199" t="s" s="2">
         <v>21</v>
@@ -27409,10 +27428,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -27435,19 +27454,17 @@
         <v>91</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N200" s="2"/>
       <c r="O200" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>21</v>
@@ -27496,7 +27513,7 @@
         <v>21</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
@@ -27511,10 +27528,10 @@
         <v>102</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>21</v>
+        <v>831</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>21</v>
@@ -27523,7 +27540,7 @@
         <v>21</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="AP200" t="s" s="2">
         <v>21</v>
@@ -27531,10 +27548,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27557,19 +27574,19 @@
         <v>91</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>21</v>
@@ -27618,7 +27635,7 @@
         <v>21</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
@@ -27636,7 +27653,7 @@
         <v>21</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>21</v>
@@ -27645,7 +27662,7 @@
         <v>21</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="AP201" t="s" s="2">
         <v>21</v>
@@ -27653,10 +27670,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27676,22 +27693,22 @@
         <v>21</v>
       </c>
       <c r="J202" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>830</v>
+        <v>150</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>831</v>
+        <v>360</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>832</v>
+        <v>361</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>833</v>
+        <v>362</v>
       </c>
       <c r="O202" t="s" s="2">
-        <v>834</v>
+        <v>363</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>21</v>
@@ -27728,17 +27745,19 @@
         <v>21</v>
       </c>
       <c r="AB202" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="AC202" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC202" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD202" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE202" t="s" s="2">
-        <v>668</v>
+        <v>21</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>829</v>
+        <v>364</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -27756,16 +27775,16 @@
         <v>21</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>835</v>
+        <v>365</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO202" t="s" s="2">
-        <v>836</v>
+        <v>366</v>
       </c>
       <c r="AP202" t="s" s="2">
         <v>21</v>
@@ -27773,14 +27792,12 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="C203" t="s" s="2">
-        <v>838</v>
-      </c>
+        <v>834</v>
+      </c>
+      <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
         <v>21</v>
       </c>
@@ -27801,19 +27818,19 @@
         <v>21</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>350</v>
+        <v>835</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>21</v>
@@ -27850,19 +27867,17 @@
         <v>21</v>
       </c>
       <c r="AB203" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC203" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="AC203" s="2"/>
       <c r="AD203" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE203" t="s" s="2">
-        <v>21</v>
+        <v>668</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
@@ -27877,10 +27892,10 @@
         <v>102</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="AM203" t="s" s="2">
         <v>154</v>
@@ -27889,7 +27904,7 @@
         <v>21</v>
       </c>
       <c r="AO203" t="s" s="2">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="AP203" t="s" s="2">
         <v>21</v>
@@ -27897,13 +27912,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="D204" t="s" s="2">
         <v>21</v>
@@ -27925,19 +27940,19 @@
         <v>21</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>841</v>
+        <v>350</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>21</v>
@@ -27986,7 +28001,7 @@
         <v>21</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -28004,7 +28019,7 @@
         <v>154</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="AM204" t="s" s="2">
         <v>154</v>
@@ -28013,7 +28028,7 @@
         <v>21</v>
       </c>
       <c r="AO204" t="s" s="2">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="AP204" t="s" s="2">
         <v>21</v>
@@ -28021,12 +28036,14 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="C205" s="2"/>
+        <v>834</v>
+      </c>
+      <c r="C205" t="s" s="2">
+        <v>845</v>
+      </c>
       <c r="D205" t="s" s="2">
         <v>21</v>
       </c>
@@ -28035,7 +28052,7 @@
         <v>81</v>
       </c>
       <c r="G205" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H205" t="s" s="2">
         <v>21</v>
@@ -28047,19 +28064,19 @@
         <v>21</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="O205" t="s" s="2">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>21</v>
@@ -28108,13 +28125,13 @@
         <v>21</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI205" t="s" s="2">
         <v>21</v>
@@ -28126,7 +28143,7 @@
         <v>154</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="AM205" t="s" s="2">
         <v>154</v>
@@ -28135,7 +28152,7 @@
         <v>21</v>
       </c>
       <c r="AO205" t="s" s="2">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="AP205" t="s" s="2">
         <v>21</v>
@@ -28143,10 +28160,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -28169,19 +28186,19 @@
         <v>21</v>
       </c>
       <c r="K206" t="s" s="2">
+        <v>848</v>
+      </c>
+      <c r="L206" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="M206" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="N206" t="s" s="2">
         <v>851</v>
       </c>
-      <c r="L206" t="s" s="2">
+      <c r="O206" t="s" s="2">
         <v>852</v>
-      </c>
-      <c r="M206" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="N206" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="O206" t="s" s="2">
-        <v>855</v>
       </c>
       <c r="P206" t="s" s="2">
         <v>21</v>
@@ -28230,7 +28247,7 @@
         <v>21</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
@@ -28242,13 +28259,13 @@
         <v>21</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>856</v>
+        <v>102</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="AM206" t="s" s="2">
         <v>154</v>
@@ -28257,7 +28274,7 @@
         <v>21</v>
       </c>
       <c r="AO206" t="s" s="2">
-        <v>21</v>
+        <v>854</v>
       </c>
       <c r="AP206" t="s" s="2">
         <v>21</v>
@@ -28265,10 +28282,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -28279,7 +28296,7 @@
         <v>81</v>
       </c>
       <c r="G207" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H207" t="s" s="2">
         <v>21</v>
@@ -28291,16 +28308,20 @@
         <v>21</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>150</v>
+        <v>856</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>151</v>
+        <v>857</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N207" s="2"/>
-      <c r="O207" s="2"/>
+        <v>858</v>
+      </c>
+      <c r="N207" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="O207" t="s" s="2">
+        <v>860</v>
+      </c>
       <c r="P207" t="s" s="2">
         <v>21</v>
       </c>
@@ -28348,28 +28369,28 @@
         <v>21</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>153</v>
+        <v>855</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH207" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI207" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>21</v>
+        <v>861</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL207" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="AM207" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AM207" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AN207" t="s" s="2">
         <v>21</v>
@@ -28383,21 +28404,21 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G208" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H208" t="s" s="2">
         <v>21</v>
@@ -28409,17 +28430,15 @@
         <v>21</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>21</v>
@@ -28468,19 +28487,19 @@
         <v>21</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH208" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI208" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>21</v>
@@ -28503,14 +28522,14 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>861</v>
+        <v>157</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
@@ -28523,26 +28542,24 @@
         <v>21</v>
       </c>
       <c r="I209" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K209" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>862</v>
+        <v>158</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>863</v>
+        <v>159</v>
       </c>
       <c r="N209" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="O209" t="s" s="2">
-        <v>226</v>
-      </c>
+      <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
         <v>21</v>
       </c>
@@ -28590,7 +28607,7 @@
         <v>21</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>864</v>
+        <v>162</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
@@ -28608,7 +28625,7 @@
         <v>21</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="AM209" t="s" s="2">
         <v>21</v>
@@ -28632,7 +28649,7 @@
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
@@ -28645,23 +28662,25 @@
         <v>21</v>
       </c>
       <c r="I210" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="N210" s="2"/>
+        <v>868</v>
+      </c>
+      <c r="N210" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O210" t="s" s="2">
-        <v>868</v>
+        <v>226</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>21</v>
@@ -28686,31 +28705,31 @@
         <v>21</v>
       </c>
       <c r="X210" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="Y210" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z210" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA210" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB210" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC210" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD210" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE210" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF210" t="s" s="2">
         <v>869</v>
-      </c>
-      <c r="Z210" t="s" s="2">
-        <v>870</v>
-      </c>
-      <c r="AA210" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB210" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC210" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD210" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE210" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF210" t="s" s="2">
-        <v>865</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
@@ -28722,22 +28741,22 @@
         <v>21</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="AM210" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO210" t="s" s="2">
-        <v>871</v>
+        <v>21</v>
       </c>
       <c r="AP210" t="s" s="2">
         <v>21</v>
@@ -28745,10 +28764,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28759,7 +28778,7 @@
         <v>81</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>21</v>
@@ -28771,16 +28790,18 @@
         <v>21</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>151</v>
+        <v>871</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>152</v>
+        <v>872</v>
       </c>
       <c r="N211" s="2"/>
-      <c r="O211" s="2"/>
+      <c r="O211" t="s" s="2">
+        <v>873</v>
+      </c>
       <c r="P211" t="s" s="2">
         <v>21</v>
       </c>
@@ -28804,13 +28825,13 @@
         <v>21</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>21</v>
+        <v>874</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>21</v>
+        <v>875</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>21</v>
@@ -28828,34 +28849,34 @@
         <v>21</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>153</v>
+        <v>870</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK211" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL211" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AM211" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM211" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AN211" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO211" t="s" s="2">
-        <v>21</v>
+        <v>876</v>
       </c>
       <c r="AP211" t="s" s="2">
         <v>21</v>
@@ -28863,21 +28884,21 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>21</v>
@@ -28889,17 +28910,15 @@
         <v>21</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N212" s="2"/>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>21</v>
@@ -28936,31 +28955,31 @@
         <v>21</v>
       </c>
       <c r="AB212" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC212" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AD212" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE212" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>21</v>
@@ -28983,14 +29002,14 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
@@ -29006,23 +29025,21 @@
         <v>21</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>301</v>
+        <v>135</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>302</v>
+        <v>158</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>303</v>
+        <v>159</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O213" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
         <v>21</v>
       </c>
@@ -29058,19 +29075,19 @@
         <v>21</v>
       </c>
       <c r="AB213" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC213" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AD213" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE213" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>306</v>
+        <v>162</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
@@ -29082,13 +29099,13 @@
         <v>21</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK213" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL213" t="s" s="2">
-        <v>307</v>
+        <v>154</v>
       </c>
       <c r="AM213" t="s" s="2">
         <v>21</v>
@@ -29097,7 +29114,7 @@
         <v>21</v>
       </c>
       <c r="AO213" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="AP213" t="s" s="2">
         <v>21</v>
@@ -29105,10 +29122,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -29119,7 +29136,7 @@
         <v>81</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H214" t="s" s="2">
         <v>21</v>
@@ -29128,19 +29145,23 @@
         <v>21</v>
       </c>
       <c r="J214" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>151</v>
+        <v>302</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N214" s="2"/>
-      <c r="O214" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="N214" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O214" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P214" t="s" s="2">
         <v>21</v>
       </c>
@@ -29188,25 +29209,25 @@
         <v>21</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>153</v>
+        <v>306</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI214" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK214" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>154</v>
+        <v>307</v>
       </c>
       <c r="AM214" t="s" s="2">
         <v>21</v>
@@ -29215,7 +29236,7 @@
         <v>21</v>
       </c>
       <c r="AO214" t="s" s="2">
-        <v>21</v>
+        <v>308</v>
       </c>
       <c r="AP214" t="s" s="2">
         <v>21</v>
@@ -29223,21 +29244,21 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G215" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H215" t="s" s="2">
         <v>21</v>
@@ -29249,17 +29270,15 @@
         <v>21</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N215" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N215" s="2"/>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>21</v>
@@ -29296,31 +29315,31 @@
         <v>21</v>
       </c>
       <c r="AB215" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC215" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AD215" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE215" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI215" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>21</v>
@@ -29343,21 +29362,21 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>21</v>
@@ -29366,23 +29385,21 @@
         <v>21</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>315</v>
+        <v>158</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>316</v>
+        <v>159</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O216" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
         <v>21</v>
       </c>
@@ -29418,37 +29435,37 @@
         <v>21</v>
       </c>
       <c r="AB216" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC216" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AD216" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE216" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>320</v>
+        <v>162</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI216" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK216" t="s" s="2">
-        <v>878</v>
+        <v>21</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>321</v>
+        <v>154</v>
       </c>
       <c r="AM216" t="s" s="2">
         <v>21</v>
@@ -29457,7 +29474,7 @@
         <v>21</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="AP216" t="s" s="2">
         <v>21</v>
@@ -29465,10 +29482,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -29491,18 +29508,20 @@
         <v>91</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O217" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="O217" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P217" t="s" s="2">
         <v>21</v>
       </c>
@@ -29550,7 +29569,7 @@
         <v>21</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -29565,10 +29584,10 @@
         <v>102</v>
       </c>
       <c r="AK217" t="s" s="2">
-        <v>21</v>
+        <v>883</v>
       </c>
       <c r="AL217" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="AM217" t="s" s="2">
         <v>21</v>
@@ -29577,7 +29596,7 @@
         <v>21</v>
       </c>
       <c r="AO217" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="AP217" t="s" s="2">
         <v>21</v>
@@ -29585,10 +29604,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29611,18 +29630,18 @@
         <v>91</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N218" s="2"/>
-      <c r="O218" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N218" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
         <v>21</v>
       </c>
@@ -29670,7 +29689,7 @@
         <v>21</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
@@ -29685,10 +29704,10 @@
         <v>102</v>
       </c>
       <c r="AK218" t="s" s="2">
-        <v>881</v>
+        <v>21</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AM218" t="s" s="2">
         <v>21</v>
@@ -29697,7 +29716,7 @@
         <v>21</v>
       </c>
       <c r="AO218" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="AP218" t="s" s="2">
         <v>21</v>
@@ -29705,10 +29724,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29731,17 +29750,17 @@
         <v>91</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="N219" s="2"/>
       <c r="O219" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="P219" t="s" s="2">
         <v>21</v>
@@ -29790,7 +29809,7 @@
         <v>21</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
@@ -29805,10 +29824,10 @@
         <v>102</v>
       </c>
       <c r="AK219" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="AL219" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AM219" t="s" s="2">
         <v>21</v>
@@ -29817,7 +29836,7 @@
         <v>21</v>
       </c>
       <c r="AO219" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AP219" t="s" s="2">
         <v>21</v>
@@ -29825,10 +29844,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29851,19 +29870,17 @@
         <v>91</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N220" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N220" s="2"/>
       <c r="O220" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>21</v>
@@ -29912,7 +29929,7 @@
         <v>21</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
@@ -29927,10 +29944,10 @@
         <v>102</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>21</v>
+        <v>888</v>
       </c>
       <c r="AL220" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="AM220" t="s" s="2">
         <v>21</v>
@@ -29939,7 +29956,7 @@
         <v>21</v>
       </c>
       <c r="AO220" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="AP220" t="s" s="2">
         <v>21</v>
@@ -29947,10 +29964,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29973,19 +29990,19 @@
         <v>91</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="N221" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="O221" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="P221" t="s" s="2">
         <v>21</v>
@@ -30034,7 +30051,7 @@
         <v>21</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>81</v>
@@ -30052,7 +30069,7 @@
         <v>21</v>
       </c>
       <c r="AL221" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="AM221" t="s" s="2">
         <v>21</v>
@@ -30061,7 +30078,7 @@
         <v>21</v>
       </c>
       <c r="AO221" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="AP221" t="s" s="2">
         <v>21</v>
@@ -30069,10 +30086,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -30092,20 +30109,22 @@
         <v>21</v>
       </c>
       <c r="J222" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>499</v>
+        <v>150</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>887</v>
+        <v>360</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="N222" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N222" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="O222" t="s" s="2">
-        <v>889</v>
+        <v>363</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>21</v>
@@ -30154,7 +30173,7 @@
         <v>21</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>886</v>
+        <v>364</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
@@ -30172,16 +30191,16 @@
         <v>21</v>
       </c>
       <c r="AL222" t="s" s="2">
-        <v>505</v>
+        <v>365</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="AN222" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO222" t="s" s="2">
-        <v>890</v>
+        <v>366</v>
       </c>
       <c r="AP222" t="s" s="2">
         <v>21</v>
@@ -30215,16 +30234,18 @@
         <v>21</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>150</v>
+        <v>499</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>151</v>
+        <v>892</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>152</v>
+        <v>893</v>
       </c>
       <c r="N223" s="2"/>
-      <c r="O223" s="2"/>
+      <c r="O223" t="s" s="2">
+        <v>894</v>
+      </c>
       <c r="P223" t="s" s="2">
         <v>21</v>
       </c>
@@ -30272,7 +30293,7 @@
         <v>21</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>153</v>
+        <v>891</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -30284,22 +30305,22 @@
         <v>21</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK223" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL223" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM223" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM223" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AN223" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO223" t="s" s="2">
-        <v>21</v>
+        <v>895</v>
       </c>
       <c r="AP223" t="s" s="2">
         <v>21</v>
@@ -30307,21 +30328,21 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G224" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H224" t="s" s="2">
         <v>21</v>
@@ -30333,17 +30354,15 @@
         <v>21</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N224" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N224" s="2"/>
       <c r="O224" s="2"/>
       <c r="P224" t="s" s="2">
         <v>21</v>
@@ -30380,31 +30399,31 @@
         <v>21</v>
       </c>
       <c r="AB224" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC224" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AD224" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE224" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH224" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI224" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ224" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK224" t="s" s="2">
         <v>21</v>
@@ -30427,46 +30446,44 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="E225" s="2"/>
       <c r="F225" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H225" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I225" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J225" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>510</v>
+        <v>158</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>511</v>
+        <v>159</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O225" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O225" s="2"/>
       <c r="P225" t="s" s="2">
         <v>21</v>
       </c>
@@ -30490,49 +30507,49 @@
         <v>21</v>
       </c>
       <c r="X225" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="Y225" t="s" s="2">
-        <v>514</v>
+        <v>21</v>
       </c>
       <c r="Z225" t="s" s="2">
-        <v>515</v>
+        <v>21</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB225" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC225" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AD225" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE225" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>516</v>
+        <v>162</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH225" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI225" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ225" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK225" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL225" t="s" s="2">
-        <v>517</v>
+        <v>154</v>
       </c>
       <c r="AM225" t="s" s="2">
         <v>21</v>
@@ -30541,7 +30558,7 @@
         <v>21</v>
       </c>
       <c r="AO225" t="s" s="2">
-        <v>518</v>
+        <v>21</v>
       </c>
       <c r="AP225" t="s" s="2">
         <v>21</v>
@@ -30549,10 +30566,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30569,25 +30586,25 @@
         <v>21</v>
       </c>
       <c r="I226" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J226" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="O226" t="s" s="2">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="P226" t="s" s="2">
         <v>21</v>
@@ -30612,13 +30629,13 @@
         <v>21</v>
       </c>
       <c r="X226" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="Y226" t="s" s="2">
-        <v>21</v>
+        <v>514</v>
       </c>
       <c r="Z226" t="s" s="2">
-        <v>21</v>
+        <v>515</v>
       </c>
       <c r="AA226" t="s" s="2">
         <v>21</v>
@@ -30636,7 +30653,7 @@
         <v>21</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
@@ -30654,7 +30671,7 @@
         <v>21</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="AM226" t="s" s="2">
         <v>21</v>
@@ -30663,7 +30680,7 @@
         <v>21</v>
       </c>
       <c r="AO226" t="s" s="2">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="AP226" t="s" s="2">
         <v>21</v>
@@ -30671,14 +30688,14 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
-        <v>528</v>
+        <v>21</v>
       </c>
       <c r="E227" s="2"/>
       <c r="F227" t="s" s="2">
@@ -30700,15 +30717,17 @@
         <v>150</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O227" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="O227" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P227" t="s" s="2">
         <v>21</v>
       </c>
@@ -30756,7 +30775,7 @@
         <v>21</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
@@ -30771,10 +30790,10 @@
         <v>102</v>
       </c>
       <c r="AK227" t="s" s="2">
-        <v>896</v>
+        <v>21</v>
       </c>
       <c r="AL227" t="s" s="2">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="AM227" t="s" s="2">
         <v>21</v>
@@ -30783,7 +30802,7 @@
         <v>21</v>
       </c>
       <c r="AO227" t="s" s="2">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="AP227" t="s" s="2">
         <v>21</v>
@@ -30791,21 +30810,21 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H228" t="s" s="2">
         <v>21</v>
@@ -30820,13 +30839,13 @@
         <v>150</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
@@ -30876,13 +30895,13 @@
         <v>21</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH228" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI228" t="s" s="2">
         <v>21</v>
@@ -30891,10 +30910,10 @@
         <v>102</v>
       </c>
       <c r="AK228" t="s" s="2">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="AL228" t="s" s="2">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="AM228" t="s" s="2">
         <v>21</v>
@@ -30903,7 +30922,7 @@
         <v>21</v>
       </c>
       <c r="AO228" t="s" s="2">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="AP228" t="s" s="2">
         <v>21</v>
@@ -30911,14 +30930,14 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
-        <v>21</v>
+        <v>537</v>
       </c>
       <c r="E229" s="2"/>
       <c r="F229" t="s" s="2">
@@ -30940,12 +30959,14 @@
         <v>150</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N229" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N229" t="s" s="2">
+        <v>540</v>
+      </c>
       <c r="O229" s="2"/>
       <c r="P229" t="s" s="2">
         <v>21</v>
@@ -30994,7 +31015,7 @@
         <v>21</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
@@ -31009,10 +31030,10 @@
         <v>102</v>
       </c>
       <c r="AK229" t="s" s="2">
-        <v>21</v>
+        <v>903</v>
       </c>
       <c r="AL229" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="AM229" t="s" s="2">
         <v>21</v>
@@ -31021,7 +31042,7 @@
         <v>21</v>
       </c>
       <c r="AO229" t="s" s="2">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="AP229" t="s" s="2">
         <v>21</v>
@@ -31029,10 +31050,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -31058,10 +31079,10 @@
         <v>150</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
@@ -31112,7 +31133,7 @@
         <v>21</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
@@ -31130,7 +31151,7 @@
         <v>21</v>
       </c>
       <c r="AL230" t="s" s="2">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="AM230" t="s" s="2">
         <v>21</v>
@@ -31139,7 +31160,7 @@
         <v>21</v>
       </c>
       <c r="AO230" t="s" s="2">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="AP230" t="s" s="2">
         <v>21</v>
@@ -31147,10 +31168,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -31161,7 +31182,7 @@
         <v>81</v>
       </c>
       <c r="G231" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H231" t="s" s="2">
         <v>21</v>
@@ -31173,18 +31194,16 @@
         <v>91</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="N231" s="2"/>
-      <c r="O231" t="s" s="2">
-        <v>562</v>
-      </c>
+      <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
         <v>21</v>
       </c>
@@ -31232,13 +31251,13 @@
         <v>21</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH231" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI231" t="s" s="2">
         <v>21</v>
@@ -31250,7 +31269,7 @@
         <v>21</v>
       </c>
       <c r="AL231" t="s" s="2">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="AM231" t="s" s="2">
         <v>21</v>
@@ -31259,7 +31278,7 @@
         <v>21</v>
       </c>
       <c r="AO231" t="s" s="2">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="AP231" t="s" s="2">
         <v>21</v>
@@ -31267,10 +31286,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -31281,7 +31300,7 @@
         <v>81</v>
       </c>
       <c r="G232" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H232" t="s" s="2">
         <v>21</v>
@@ -31290,22 +31309,20 @@
         <v>21</v>
       </c>
       <c r="J232" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>567</v>
+        <v>193</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>903</v>
+        <v>560</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>904</v>
-      </c>
-      <c r="N232" t="s" s="2">
-        <v>905</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N232" s="2"/>
       <c r="O232" t="s" s="2">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>21</v>
@@ -31354,13 +31371,13 @@
         <v>21</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>902</v>
+        <v>563</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH232" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI232" t="s" s="2">
         <v>21</v>
@@ -31372,16 +31389,16 @@
         <v>21</v>
       </c>
       <c r="AL232" t="s" s="2">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="AM232" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="AN232" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO232" t="s" s="2">
-        <v>906</v>
+        <v>565</v>
       </c>
       <c r="AP232" t="s" s="2">
         <v>21</v>
@@ -31403,7 +31420,7 @@
         <v>81</v>
       </c>
       <c r="G233" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H233" t="s" s="2">
         <v>21</v>
@@ -31415,16 +31432,20 @@
         <v>21</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>150</v>
+        <v>567</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>151</v>
+        <v>908</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N233" s="2"/>
-      <c r="O233" s="2"/>
+        <v>909</v>
+      </c>
+      <c r="N233" t="s" s="2">
+        <v>910</v>
+      </c>
+      <c r="O233" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="P233" t="s" s="2">
         <v>21</v>
       </c>
@@ -31472,34 +31493,34 @@
         <v>21</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>153</v>
+        <v>907</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH233" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI233" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ233" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK233" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL233" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AM233" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM233" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AN233" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO233" t="s" s="2">
-        <v>21</v>
+        <v>911</v>
       </c>
       <c r="AP233" t="s" s="2">
         <v>21</v>
@@ -31507,21 +31528,21 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="E234" s="2"/>
       <c r="F234" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G234" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H234" t="s" s="2">
         <v>21</v>
@@ -31533,17 +31554,15 @@
         <v>21</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N234" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N234" s="2"/>
       <c r="O234" s="2"/>
       <c r="P234" t="s" s="2">
         <v>21</v>
@@ -31580,31 +31599,31 @@
         <v>21</v>
       </c>
       <c r="AB234" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC234" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AD234" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE234" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH234" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI234" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ234" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK234" t="s" s="2">
         <v>21</v>
@@ -31627,21 +31646,21 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="E235" s="2"/>
       <c r="F235" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G235" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H235" t="s" s="2">
         <v>21</v>
@@ -31650,18 +31669,20 @@
         <v>21</v>
       </c>
       <c r="J235" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>578</v>
+        <v>158</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N235" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N235" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O235" s="2"/>
       <c r="P235" t="s" s="2">
         <v>21</v>
@@ -31686,49 +31707,49 @@
         <v>21</v>
       </c>
       <c r="X235" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="Y235" t="s" s="2">
-        <v>580</v>
+        <v>21</v>
       </c>
       <c r="Z235" t="s" s="2">
-        <v>581</v>
+        <v>21</v>
       </c>
       <c r="AA235" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB235" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC235" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AD235" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE235" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>582</v>
+        <v>162</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH235" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI235" t="s" s="2">
-        <v>583</v>
+        <v>21</v>
       </c>
       <c r="AJ235" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK235" t="s" s="2">
-        <v>910</v>
+        <v>21</v>
       </c>
       <c r="AL235" t="s" s="2">
-        <v>585</v>
+        <v>154</v>
       </c>
       <c r="AM235" t="s" s="2">
         <v>21</v>
@@ -31737,7 +31758,7 @@
         <v>21</v>
       </c>
       <c r="AO235" t="s" s="2">
-        <v>586</v>
+        <v>21</v>
       </c>
       <c r="AP235" t="s" s="2">
         <v>21</v>
@@ -31745,10 +31766,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -31771,20 +31792,16 @@
         <v>91</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N236" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>591</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="N236" s="2"/>
+      <c r="O236" s="2"/>
       <c r="P236" t="s" s="2">
         <v>21</v>
       </c>
@@ -31808,13 +31825,13 @@
         <v>21</v>
       </c>
       <c r="X236" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="Y236" t="s" s="2">
-        <v>21</v>
+        <v>580</v>
       </c>
       <c r="Z236" t="s" s="2">
-        <v>21</v>
+        <v>581</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>21</v>
@@ -31832,7 +31849,7 @@
         <v>21</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>81</v>
@@ -31841,16 +31858,16 @@
         <v>90</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>21</v>
+        <v>583</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK236" t="s" s="2">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="AL236" t="s" s="2">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="AM236" t="s" s="2">
         <v>21</v>
@@ -31859,7 +31876,7 @@
         <v>21</v>
       </c>
       <c r="AO236" t="s" s="2">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="AP236" t="s" s="2">
         <v>21</v>
@@ -31867,10 +31884,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -31887,25 +31904,25 @@
         <v>21</v>
       </c>
       <c r="I237" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J237" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="O237" t="s" s="2">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="P237" t="s" s="2">
         <v>21</v>
@@ -31930,13 +31947,13 @@
         <v>21</v>
       </c>
       <c r="X237" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="Y237" t="s" s="2">
-        <v>600</v>
+        <v>21</v>
       </c>
       <c r="Z237" t="s" s="2">
-        <v>601</v>
+        <v>21</v>
       </c>
       <c r="AA237" t="s" s="2">
         <v>21</v>
@@ -31954,7 +31971,7 @@
         <v>21</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>81</v>
@@ -31969,10 +31986,10 @@
         <v>102</v>
       </c>
       <c r="AK237" t="s" s="2">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="AL237" t="s" s="2">
-        <v>517</v>
+        <v>593</v>
       </c>
       <c r="AM237" t="s" s="2">
         <v>21</v>
@@ -31981,7 +31998,7 @@
         <v>21</v>
       </c>
       <c r="AO237" t="s" s="2">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="AP237" t="s" s="2">
         <v>21</v>
@@ -31989,10 +32006,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -32009,24 +32026,26 @@
         <v>21</v>
       </c>
       <c r="I238" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J238" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>606</v>
+        <v>110</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="N238" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="O238" s="2"/>
+        <v>598</v>
+      </c>
+      <c r="O238" t="s" s="2">
+        <v>599</v>
+      </c>
       <c r="P238" t="s" s="2">
         <v>21</v>
       </c>
@@ -32050,13 +32069,13 @@
         <v>21</v>
       </c>
       <c r="X238" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="Y238" t="s" s="2">
-        <v>21</v>
+        <v>600</v>
       </c>
       <c r="Z238" t="s" s="2">
-        <v>21</v>
+        <v>601</v>
       </c>
       <c r="AA238" t="s" s="2">
         <v>21</v>
@@ -32074,7 +32093,7 @@
         <v>21</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>81</v>
@@ -32089,10 +32108,10 @@
         <v>102</v>
       </c>
       <c r="AK238" t="s" s="2">
-        <v>21</v>
+        <v>919</v>
       </c>
       <c r="AL238" t="s" s="2">
-        <v>154</v>
+        <v>517</v>
       </c>
       <c r="AM238" t="s" s="2">
         <v>21</v>
@@ -32101,7 +32120,7 @@
         <v>21</v>
       </c>
       <c r="AO238" t="s" s="2">
-        <v>154</v>
+        <v>604</v>
       </c>
       <c r="AP238" t="s" s="2">
         <v>21</v>
@@ -32109,10 +32128,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -32135,15 +32154,17 @@
         <v>91</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>193</v>
+        <v>606</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N239" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="N239" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="O239" s="2"/>
       <c r="P239" t="s" s="2">
         <v>21</v>
@@ -32192,7 +32213,7 @@
         <v>21</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>81</v>
@@ -32210,7 +32231,7 @@
         <v>21</v>
       </c>
       <c r="AL239" t="s" s="2">
-        <v>564</v>
+        <v>154</v>
       </c>
       <c r="AM239" t="s" s="2">
         <v>21</v>
@@ -32219,7 +32240,7 @@
         <v>21</v>
       </c>
       <c r="AO239" t="s" s="2">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="AP239" t="s" s="2">
         <v>21</v>
@@ -32227,10 +32248,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -32250,21 +32271,19 @@
         <v>21</v>
       </c>
       <c r="J240" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>918</v>
+        <v>612</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>919</v>
+        <v>613</v>
       </c>
       <c r="N240" s="2"/>
-      <c r="O240" t="s" s="2">
-        <v>920</v>
-      </c>
+      <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
         <v>21</v>
       </c>
@@ -32312,7 +32331,7 @@
         <v>21</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>917</v>
+        <v>614</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>81</v>
@@ -32324,22 +32343,22 @@
         <v>21</v>
       </c>
       <c r="AJ240" t="s" s="2">
-        <v>222</v>
+        <v>102</v>
       </c>
       <c r="AK240" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL240" t="s" s="2">
-        <v>683</v>
+        <v>564</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="AN240" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO240" t="s" s="2">
-        <v>921</v>
+        <v>133</v>
       </c>
       <c r="AP240" t="s" s="2">
         <v>21</v>
@@ -32373,16 +32392,18 @@
         <v>21</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>150</v>
+        <v>221</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>151</v>
+        <v>923</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>152</v>
+        <v>924</v>
       </c>
       <c r="N241" s="2"/>
-      <c r="O241" s="2"/>
+      <c r="O241" t="s" s="2">
+        <v>925</v>
+      </c>
       <c r="P241" t="s" s="2">
         <v>21</v>
       </c>
@@ -32430,7 +32451,7 @@
         <v>21</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>153</v>
+        <v>922</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>81</v>
@@ -32442,22 +32463,22 @@
         <v>21</v>
       </c>
       <c r="AJ241" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AK241" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL241" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AM241" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM241" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AN241" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO241" t="s" s="2">
-        <v>21</v>
+        <v>926</v>
       </c>
       <c r="AP241" t="s" s="2">
         <v>21</v>
@@ -32465,21 +32486,21 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="E242" s="2"/>
       <c r="F242" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G242" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H242" t="s" s="2">
         <v>21</v>
@@ -32491,17 +32512,15 @@
         <v>21</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N242" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N242" s="2"/>
       <c r="O242" s="2"/>
       <c r="P242" t="s" s="2">
         <v>21</v>
@@ -32538,31 +32557,31 @@
         <v>21</v>
       </c>
       <c r="AB242" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC242" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AD242" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE242" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH242" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI242" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ242" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK242" t="s" s="2">
         <v>21</v>
@@ -32585,23 +32604,21 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>923</v>
-      </c>
-      <c r="C243" t="s" s="2">
-        <v>689</v>
-      </c>
+        <v>928</v>
+      </c>
+      <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="E243" s="2"/>
       <c r="F243" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G243" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H243" t="s" s="2">
         <v>21</v>
@@ -32613,15 +32630,17 @@
         <v>21</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>690</v>
+        <v>135</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>691</v>
+        <v>158</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="N243" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N243" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O243" s="2"/>
       <c r="P243" t="s" s="2">
         <v>21</v>
@@ -32658,16 +32677,16 @@
         <v>21</v>
       </c>
       <c r="AB243" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC243" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AD243" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE243" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF243" t="s" s="2">
         <v>162</v>
@@ -32688,7 +32707,7 @@
         <v>21</v>
       </c>
       <c r="AL243" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="AM243" t="s" s="2">
         <v>21</v>
@@ -32705,12 +32724,14 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>925</v>
-      </c>
-      <c r="C244" s="2"/>
+        <v>928</v>
+      </c>
+      <c r="C244" t="s" s="2">
+        <v>689</v>
+      </c>
       <c r="D244" t="s" s="2">
         <v>21</v>
       </c>
@@ -32725,26 +32746,22 @@
         <v>21</v>
       </c>
       <c r="I244" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J244" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>110</v>
+        <v>690</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="N244" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="O244" t="s" s="2">
-        <v>697</v>
-      </c>
+        <v>692</v>
+      </c>
+      <c r="N244" s="2"/>
+      <c r="O244" s="2"/>
       <c r="P244" t="s" s="2">
         <v>21</v>
       </c>
@@ -32756,7 +32773,7 @@
         <v>21</v>
       </c>
       <c r="T244" t="s" s="2">
-        <v>698</v>
+        <v>21</v>
       </c>
       <c r="U244" t="s" s="2">
         <v>21</v>
@@ -32768,13 +32785,13 @@
         <v>21</v>
       </c>
       <c r="X244" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="Y244" t="s" s="2">
-        <v>699</v>
+        <v>21</v>
       </c>
       <c r="Z244" t="s" s="2">
-        <v>700</v>
+        <v>21</v>
       </c>
       <c r="AA244" t="s" s="2">
         <v>21</v>
@@ -32792,25 +32809,25 @@
         <v>21</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>701</v>
+        <v>162</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH244" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI244" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ244" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK244" t="s" s="2">
-        <v>926</v>
+        <v>21</v>
       </c>
       <c r="AL244" t="s" s="2">
-        <v>517</v>
+        <v>21</v>
       </c>
       <c r="AM244" t="s" s="2">
         <v>21</v>
@@ -32819,7 +32836,7 @@
         <v>21</v>
       </c>
       <c r="AO244" t="s" s="2">
-        <v>703</v>
+        <v>21</v>
       </c>
       <c r="AP244" t="s" s="2">
         <v>21</v>
@@ -32827,12 +32844,14 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>927</v>
-      </c>
-      <c r="C245" s="2"/>
+        <v>928</v>
+      </c>
+      <c r="C245" t="s" s="2">
+        <v>694</v>
+      </c>
       <c r="D245" t="s" s="2">
         <v>21</v>
       </c>
@@ -32850,20 +32869,18 @@
         <v>21</v>
       </c>
       <c r="J245" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>110</v>
+        <v>695</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="N245" t="s" s="2">
-        <v>707</v>
-      </c>
+        <v>697</v>
+      </c>
+      <c r="N245" s="2"/>
       <c r="O245" s="2"/>
       <c r="P245" t="s" s="2">
         <v>21</v>
@@ -32876,7 +32893,7 @@
         <v>21</v>
       </c>
       <c r="T245" t="s" s="2">
-        <v>708</v>
+        <v>21</v>
       </c>
       <c r="U245" t="s" s="2">
         <v>21</v>
@@ -32888,13 +32905,13 @@
         <v>21</v>
       </c>
       <c r="X245" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="Y245" t="s" s="2">
-        <v>709</v>
+        <v>21</v>
       </c>
       <c r="Z245" t="s" s="2">
-        <v>710</v>
+        <v>21</v>
       </c>
       <c r="AA245" t="s" s="2">
         <v>21</v>
@@ -32912,25 +32929,25 @@
         <v>21</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>711</v>
+        <v>162</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH245" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI245" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ245" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK245" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL245" t="s" s="2">
-        <v>517</v>
+        <v>21</v>
       </c>
       <c r="AM245" t="s" s="2">
         <v>21</v>
@@ -32939,7 +32956,7 @@
         <v>21</v>
       </c>
       <c r="AO245" t="s" s="2">
-        <v>712</v>
+        <v>21</v>
       </c>
       <c r="AP245" t="s" s="2">
         <v>21</v>
@@ -32947,10 +32964,10 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -32967,25 +32984,25 @@
         <v>21</v>
       </c>
       <c r="I246" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J246" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>714</v>
+        <v>699</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="O246" t="s" s="2">
-        <v>523</v>
+        <v>702</v>
       </c>
       <c r="P246" t="s" s="2">
         <v>21</v>
@@ -32998,7 +33015,7 @@
         <v>21</v>
       </c>
       <c r="T246" t="s" s="2">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="U246" t="s" s="2">
         <v>21</v>
@@ -33010,13 +33027,13 @@
         <v>21</v>
       </c>
       <c r="X246" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="Y246" t="s" s="2">
-        <v>21</v>
+        <v>704</v>
       </c>
       <c r="Z246" t="s" s="2">
-        <v>21</v>
+        <v>705</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>21</v>
@@ -33034,7 +33051,7 @@
         <v>21</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>81</v>
@@ -33049,10 +33066,10 @@
         <v>102</v>
       </c>
       <c r="AK246" t="s" s="2">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="AL246" t="s" s="2">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="AM246" t="s" s="2">
         <v>21</v>
@@ -33061,7 +33078,7 @@
         <v>21</v>
       </c>
       <c r="AO246" t="s" s="2">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="AP246" t="s" s="2">
         <v>21</v>
@@ -33069,10 +33086,10 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -33083,7 +33100,7 @@
         <v>81</v>
       </c>
       <c r="G247" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H247" t="s" s="2">
         <v>21</v>
@@ -33095,15 +33112,17 @@
         <v>91</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="N247" s="2"/>
+        <v>711</v>
+      </c>
+      <c r="N247" t="s" s="2">
+        <v>712</v>
+      </c>
       <c r="O247" s="2"/>
       <c r="P247" t="s" s="2">
         <v>21</v>
@@ -33116,7 +33135,7 @@
         <v>21</v>
       </c>
       <c r="T247" t="s" s="2">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="U247" t="s" s="2">
         <v>21</v>
@@ -33128,13 +33147,13 @@
         <v>21</v>
       </c>
       <c r="X247" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="Y247" t="s" s="2">
-        <v>21</v>
+        <v>714</v>
       </c>
       <c r="Z247" t="s" s="2">
-        <v>21</v>
+        <v>715</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>21</v>
@@ -33152,13 +33171,13 @@
         <v>21</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH247" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI247" t="s" s="2">
         <v>21</v>
@@ -33167,10 +33186,10 @@
         <v>102</v>
       </c>
       <c r="AK247" t="s" s="2">
-        <v>931</v>
+        <v>21</v>
       </c>
       <c r="AL247" t="s" s="2">
-        <v>727</v>
+        <v>517</v>
       </c>
       <c r="AM247" t="s" s="2">
         <v>21</v>
@@ -33179,7 +33198,7 @@
         <v>21</v>
       </c>
       <c r="AO247" t="s" s="2">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="AP247" t="s" s="2">
         <v>21</v>
@@ -33187,10 +33206,10 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -33210,19 +33229,23 @@
         <v>21</v>
       </c>
       <c r="J248" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K248" t="s" s="2">
         <v>150</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>627</v>
+        <v>719</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N248" s="2"/>
-      <c r="O248" s="2"/>
+        <v>720</v>
+      </c>
+      <c r="N248" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="O248" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P248" t="s" s="2">
         <v>21</v>
       </c>
@@ -33234,7 +33257,7 @@
         <v>21</v>
       </c>
       <c r="T248" t="s" s="2">
-        <v>21</v>
+        <v>722</v>
       </c>
       <c r="U248" t="s" s="2">
         <v>21</v>
@@ -33270,7 +33293,7 @@
         <v>21</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>153</v>
+        <v>723</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>81</v>
@@ -33282,13 +33305,13 @@
         <v>21</v>
       </c>
       <c r="AJ248" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK248" t="s" s="2">
-        <v>21</v>
+        <v>935</v>
       </c>
       <c r="AL248" t="s" s="2">
-        <v>21</v>
+        <v>525</v>
       </c>
       <c r="AM248" t="s" s="2">
         <v>21</v>
@@ -33297,7 +33320,7 @@
         <v>21</v>
       </c>
       <c r="AO248" t="s" s="2">
-        <v>21</v>
+        <v>725</v>
       </c>
       <c r="AP248" t="s" s="2">
         <v>21</v>
@@ -33305,10 +33328,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -33328,16 +33351,16 @@
         <v>21</v>
       </c>
       <c r="J249" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>136</v>
+        <v>727</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>137</v>
+        <v>728</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" s="2"/>
@@ -33352,7 +33375,7 @@
         <v>21</v>
       </c>
       <c r="T249" t="s" s="2">
-        <v>21</v>
+        <v>729</v>
       </c>
       <c r="U249" t="s" s="2">
         <v>21</v>
@@ -33376,17 +33399,19 @@
         <v>21</v>
       </c>
       <c r="AB249" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC249" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC249" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD249" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE249" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>162</v>
+        <v>730</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>81</v>
@@ -33398,13 +33423,13 @@
         <v>21</v>
       </c>
       <c r="AJ249" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK249" t="s" s="2">
-        <v>21</v>
+        <v>937</v>
       </c>
       <c r="AL249" t="s" s="2">
-        <v>21</v>
+        <v>732</v>
       </c>
       <c r="AM249" t="s" s="2">
         <v>21</v>
@@ -33413,7 +33438,7 @@
         <v>21</v>
       </c>
       <c r="AO249" t="s" s="2">
-        <v>21</v>
+        <v>733</v>
       </c>
       <c r="AP249" t="s" s="2">
         <v>21</v>
@@ -33421,14 +33446,12 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>933</v>
-      </c>
-      <c r="C250" t="s" s="2">
-        <v>732</v>
-      </c>
+        <v>938</v>
+      </c>
+      <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
         <v>21</v>
       </c>
@@ -33449,13 +33472,13 @@
         <v>21</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>733</v>
+        <v>150</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>734</v>
+        <v>627</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>735</v>
+        <v>628</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" s="2"/>
@@ -33506,25 +33529,25 @@
         <v>21</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH250" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI250" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="AJ250" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK250" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL250" t="s" s="2">
-        <v>736</v>
+        <v>21</v>
       </c>
       <c r="AM250" t="s" s="2">
         <v>21</v>
@@ -33541,14 +33564,12 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>933</v>
-      </c>
-      <c r="C251" t="s" s="2">
-        <v>738</v>
-      </c>
+        <v>939</v>
+      </c>
+      <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
         <v>21</v>
       </c>
@@ -33557,7 +33578,7 @@
         <v>81</v>
       </c>
       <c r="G251" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H251" t="s" s="2">
         <v>21</v>
@@ -33569,13 +33590,13 @@
         <v>21</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>739</v>
+        <v>135</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>740</v>
+        <v>136</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>741</v>
+        <v>137</v>
       </c>
       <c r="N251" s="2"/>
       <c r="O251" s="2"/>
@@ -33614,16 +33635,14 @@
         <v>21</v>
       </c>
       <c r="AB251" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC251" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC251" s="2"/>
       <c r="AD251" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE251" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF251" t="s" s="2">
         <v>162</v>
@@ -33635,7 +33654,7 @@
         <v>82</v>
       </c>
       <c r="AI251" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="AJ251" t="s" s="2">
         <v>141</v>
@@ -33644,7 +33663,7 @@
         <v>21</v>
       </c>
       <c r="AL251" t="s" s="2">
-        <v>742</v>
+        <v>21</v>
       </c>
       <c r="AM251" t="s" s="2">
         <v>21</v>
@@ -33661,13 +33680,13 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="D252" t="s" s="2">
         <v>21</v>
@@ -33689,13 +33708,13 @@
         <v>21</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="N252" s="2"/>
       <c r="O252" s="2"/>
@@ -33764,7 +33783,7 @@
         <v>21</v>
       </c>
       <c r="AL252" t="s" s="2">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="AM252" t="s" s="2">
         <v>21</v>
@@ -33781,13 +33800,13 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>933</v>
+        <v>939</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="D253" t="s" s="2">
         <v>21</v>
@@ -33809,13 +33828,13 @@
         <v>21</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="N253" s="2"/>
       <c r="O253" s="2"/>
@@ -33884,7 +33903,7 @@
         <v>21</v>
       </c>
       <c r="AL253" t="s" s="2">
-        <v>21</v>
+        <v>747</v>
       </c>
       <c r="AM253" t="s" s="2">
         <v>21</v>
@@ -33901,12 +33920,14 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>938</v>
-      </c>
-      <c r="C254" s="2"/>
+        <v>939</v>
+      </c>
+      <c r="C254" t="s" s="2">
+        <v>749</v>
+      </c>
       <c r="D254" t="s" s="2">
         <v>21</v>
       </c>
@@ -33927,13 +33948,13 @@
         <v>21</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>150</v>
+        <v>750</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>659</v>
+        <v>751</v>
       </c>
       <c r="N254" s="2"/>
       <c r="O254" s="2"/>
@@ -33957,7 +33978,7 @@
         <v>21</v>
       </c>
       <c r="W254" t="s" s="2">
-        <v>755</v>
+        <v>21</v>
       </c>
       <c r="X254" t="s" s="2">
         <v>21</v>
@@ -33984,25 +34005,25 @@
         <v>21</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>637</v>
+        <v>162</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH254" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI254" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="AJ254" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK254" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL254" t="s" s="2">
-        <v>21</v>
+        <v>752</v>
       </c>
       <c r="AM254" t="s" s="2">
         <v>21</v>
@@ -34019,14 +34040,16 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>939</v>
       </c>
-      <c r="C255" s="2"/>
+      <c r="C255" t="s" s="2">
+        <v>754</v>
+      </c>
       <c r="D255" t="s" s="2">
-        <v>757</v>
+        <v>21</v>
       </c>
       <c r="E255" s="2"/>
       <c r="F255" t="s" s="2">
@@ -34042,16 +34065,16 @@
         <v>21</v>
       </c>
       <c r="J255" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>150</v>
+        <v>755</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="N255" s="2"/>
       <c r="O255" s="2"/>
@@ -34066,7 +34089,7 @@
         <v>21</v>
       </c>
       <c r="T255" t="s" s="2">
-        <v>760</v>
+        <v>21</v>
       </c>
       <c r="U255" t="s" s="2">
         <v>21</v>
@@ -34102,25 +34125,25 @@
         <v>21</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>761</v>
+        <v>162</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH255" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI255" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="AJ255" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK255" t="s" s="2">
-        <v>940</v>
+        <v>21</v>
       </c>
       <c r="AL255" t="s" s="2">
-        <v>763</v>
+        <v>21</v>
       </c>
       <c r="AM255" t="s" s="2">
         <v>21</v>
@@ -34129,7 +34152,7 @@
         <v>21</v>
       </c>
       <c r="AO255" t="s" s="2">
-        <v>764</v>
+        <v>21</v>
       </c>
       <c r="AP255" t="s" s="2">
         <v>21</v>
@@ -34137,21 +34160,21 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
-        <v>766</v>
+        <v>21</v>
       </c>
       <c r="E256" s="2"/>
       <c r="F256" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G256" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H256" t="s" s="2">
         <v>21</v>
@@ -34160,20 +34183,18 @@
         <v>21</v>
       </c>
       <c r="J256" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K256" t="s" s="2">
         <v>150</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="N256" t="s" s="2">
-        <v>769</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="N256" s="2"/>
       <c r="O256" s="2"/>
       <c r="P256" t="s" s="2">
         <v>21</v>
@@ -34186,7 +34207,7 @@
         <v>21</v>
       </c>
       <c r="T256" t="s" s="2">
-        <v>770</v>
+        <v>21</v>
       </c>
       <c r="U256" t="s" s="2">
         <v>21</v>
@@ -34195,7 +34216,7 @@
         <v>21</v>
       </c>
       <c r="W256" t="s" s="2">
-        <v>21</v>
+        <v>760</v>
       </c>
       <c r="X256" t="s" s="2">
         <v>21</v>
@@ -34222,7 +34243,7 @@
         <v>21</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>771</v>
+        <v>637</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>81</v>
@@ -34234,13 +34255,13 @@
         <v>21</v>
       </c>
       <c r="AJ256" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK256" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL256" t="s" s="2">
-        <v>772</v>
+        <v>21</v>
       </c>
       <c r="AM256" t="s" s="2">
         <v>21</v>
@@ -34249,7 +34270,7 @@
         <v>21</v>
       </c>
       <c r="AO256" t="s" s="2">
-        <v>773</v>
+        <v>21</v>
       </c>
       <c r="AP256" t="s" s="2">
         <v>21</v>
@@ -34257,14 +34278,14 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
-        <v>775</v>
+        <v>762</v>
       </c>
       <c r="E257" s="2"/>
       <c r="F257" t="s" s="2">
@@ -34286,10 +34307,10 @@
         <v>150</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="N257" s="2"/>
       <c r="O257" s="2"/>
@@ -34304,7 +34325,7 @@
         <v>21</v>
       </c>
       <c r="T257" t="s" s="2">
-        <v>21</v>
+        <v>765</v>
       </c>
       <c r="U257" t="s" s="2">
         <v>21</v>
@@ -34340,7 +34361,7 @@
         <v>21</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>81</v>
@@ -34355,10 +34376,10 @@
         <v>102</v>
       </c>
       <c r="AK257" t="s" s="2">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="AL257" t="s" s="2">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="AM257" t="s" s="2">
         <v>21</v>
@@ -34367,7 +34388,7 @@
         <v>21</v>
       </c>
       <c r="AO257" t="s" s="2">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="AP257" t="s" s="2">
         <v>21</v>
@@ -34375,21 +34396,21 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="E258" s="2"/>
       <c r="F258" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G258" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H258" t="s" s="2">
         <v>21</v>
@@ -34404,12 +34425,14 @@
         <v>150</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>784</v>
+        <v>772</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="N258" s="2"/>
+        <v>773</v>
+      </c>
+      <c r="N258" t="s" s="2">
+        <v>774</v>
+      </c>
       <c r="O258" s="2"/>
       <c r="P258" t="s" s="2">
         <v>21</v>
@@ -34422,7 +34445,7 @@
         <v>21</v>
       </c>
       <c r="T258" t="s" s="2">
-        <v>786</v>
+        <v>775</v>
       </c>
       <c r="U258" t="s" s="2">
         <v>21</v>
@@ -34458,7 +34481,7 @@
         <v>21</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>81</v>
@@ -34473,10 +34496,10 @@
         <v>102</v>
       </c>
       <c r="AK258" t="s" s="2">
-        <v>945</v>
+        <v>21</v>
       </c>
       <c r="AL258" t="s" s="2">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="AM258" t="s" s="2">
         <v>21</v>
@@ -34485,7 +34508,7 @@
         <v>21</v>
       </c>
       <c r="AO258" t="s" s="2">
-        <v>790</v>
+        <v>778</v>
       </c>
       <c r="AP258" t="s" s="2">
         <v>21</v>
@@ -34493,14 +34516,14 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
-        <v>21</v>
+        <v>780</v>
       </c>
       <c r="E259" s="2"/>
       <c r="F259" t="s" s="2">
@@ -34522,14 +34545,12 @@
         <v>150</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="N259" t="s" s="2">
-        <v>794</v>
-      </c>
+        <v>782</v>
+      </c>
+      <c r="N259" s="2"/>
       <c r="O259" s="2"/>
       <c r="P259" t="s" s="2">
         <v>21</v>
@@ -34578,7 +34599,7 @@
         <v>21</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>81</v>
@@ -34593,10 +34614,10 @@
         <v>102</v>
       </c>
       <c r="AK259" t="s" s="2">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="AL259" t="s" s="2">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="AM259" t="s" s="2">
         <v>21</v>
@@ -34605,7 +34626,7 @@
         <v>21</v>
       </c>
       <c r="AO259" t="s" s="2">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="AP259" t="s" s="2">
         <v>21</v>
@@ -34613,21 +34634,21 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
-        <v>21</v>
+        <v>788</v>
       </c>
       <c r="E260" s="2"/>
       <c r="F260" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G260" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H260" t="s" s="2">
         <v>21</v>
@@ -34639,18 +34660,16 @@
         <v>91</v>
       </c>
       <c r="K260" t="s" s="2">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="L260" t="s" s="2">
-        <v>800</v>
+        <v>789</v>
       </c>
       <c r="M260" t="s" s="2">
-        <v>801</v>
+        <v>790</v>
       </c>
       <c r="N260" s="2"/>
-      <c r="O260" t="s" s="2">
-        <v>802</v>
-      </c>
+      <c r="O260" s="2"/>
       <c r="P260" t="s" s="2">
         <v>21</v>
       </c>
@@ -34662,7 +34681,7 @@
         <v>21</v>
       </c>
       <c r="T260" t="s" s="2">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="U260" t="s" s="2">
         <v>21</v>
@@ -34698,7 +34717,7 @@
         <v>21</v>
       </c>
       <c r="AF260" t="s" s="2">
-        <v>804</v>
+        <v>792</v>
       </c>
       <c r="AG260" t="s" s="2">
         <v>81</v>
@@ -34713,10 +34732,10 @@
         <v>102</v>
       </c>
       <c r="AK260" t="s" s="2">
-        <v>21</v>
+        <v>951</v>
       </c>
       <c r="AL260" t="s" s="2">
-        <v>564</v>
+        <v>794</v>
       </c>
       <c r="AM260" t="s" s="2">
         <v>21</v>
@@ -34725,7 +34744,7 @@
         <v>21</v>
       </c>
       <c r="AO260" t="s" s="2">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="AP260" t="s" s="2">
         <v>21</v>
@@ -34733,10 +34752,10 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -34756,21 +34775,21 @@
         <v>21</v>
       </c>
       <c r="J261" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K261" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>616</v>
+        <v>797</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>950</v>
-      </c>
-      <c r="N261" s="2"/>
-      <c r="O261" t="s" s="2">
-        <v>951</v>
-      </c>
+        <v>798</v>
+      </c>
+      <c r="N261" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="O261" s="2"/>
       <c r="P261" t="s" s="2">
         <v>21</v>
       </c>
@@ -34794,13 +34813,13 @@
         <v>21</v>
       </c>
       <c r="X261" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="Y261" t="s" s="2">
-        <v>620</v>
+        <v>21</v>
       </c>
       <c r="Z261" t="s" s="2">
-        <v>621</v>
+        <v>21</v>
       </c>
       <c r="AA261" t="s" s="2">
         <v>21</v>
@@ -34818,7 +34837,7 @@
         <v>21</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>949</v>
+        <v>800</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>81</v>
@@ -34833,19 +34852,19 @@
         <v>102</v>
       </c>
       <c r="AK261" t="s" s="2">
-        <v>154</v>
+        <v>953</v>
       </c>
       <c r="AL261" t="s" s="2">
-        <v>623</v>
+        <v>802</v>
       </c>
       <c r="AM261" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="AN261" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO261" t="s" s="2">
-        <v>952</v>
+        <v>803</v>
       </c>
       <c r="AP261" t="s" s="2">
         <v>21</v>
@@ -34853,10 +34872,10 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -34867,7 +34886,7 @@
         <v>81</v>
       </c>
       <c r="G262" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H262" t="s" s="2">
         <v>21</v>
@@ -34876,19 +34895,21 @@
         <v>21</v>
       </c>
       <c r="J262" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>627</v>
+        <v>805</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>628</v>
+        <v>806</v>
       </c>
       <c r="N262" s="2"/>
-      <c r="O262" s="2"/>
+      <c r="O262" t="s" s="2">
+        <v>807</v>
+      </c>
       <c r="P262" t="s" s="2">
         <v>21</v>
       </c>
@@ -34900,7 +34921,7 @@
         <v>21</v>
       </c>
       <c r="T262" t="s" s="2">
-        <v>21</v>
+        <v>808</v>
       </c>
       <c r="U262" t="s" s="2">
         <v>21</v>
@@ -34936,7 +34957,7 @@
         <v>21</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>153</v>
+        <v>809</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>81</v>
@@ -34948,13 +34969,13 @@
         <v>21</v>
       </c>
       <c r="AJ262" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK262" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL262" t="s" s="2">
-        <v>21</v>
+        <v>564</v>
       </c>
       <c r="AM262" t="s" s="2">
         <v>21</v>
@@ -34963,7 +34984,7 @@
         <v>21</v>
       </c>
       <c r="AO262" t="s" s="2">
-        <v>21</v>
+        <v>810</v>
       </c>
       <c r="AP262" t="s" s="2">
         <v>21</v>
@@ -34971,10 +34992,10 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -34985,7 +35006,7 @@
         <v>81</v>
       </c>
       <c r="G263" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H263" t="s" s="2">
         <v>21</v>
@@ -34997,16 +35018,18 @@
         <v>21</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>136</v>
+        <v>616</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>137</v>
+        <v>956</v>
       </c>
       <c r="N263" s="2"/>
-      <c r="O263" s="2"/>
+      <c r="O263" t="s" s="2">
+        <v>957</v>
+      </c>
       <c r="P263" t="s" s="2">
         <v>21</v>
       </c>
@@ -35030,56 +35053,58 @@
         <v>21</v>
       </c>
       <c r="X263" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="Y263" t="s" s="2">
-        <v>21</v>
+        <v>620</v>
       </c>
       <c r="Z263" t="s" s="2">
-        <v>21</v>
+        <v>621</v>
       </c>
       <c r="AA263" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB263" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC263" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC263" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD263" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE263" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>162</v>
+        <v>955</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH263" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI263" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ263" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK263" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="AL263" t="s" s="2">
-        <v>21</v>
+        <v>623</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="AN263" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO263" t="s" s="2">
-        <v>21</v>
+        <v>958</v>
       </c>
       <c r="AP263" t="s" s="2">
         <v>21</v>
@@ -35087,14 +35112,12 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>954</v>
-      </c>
-      <c r="C264" t="s" s="2">
-        <v>631</v>
-      </c>
+        <v>959</v>
+      </c>
+      <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
         <v>21</v>
       </c>
@@ -35115,13 +35138,13 @@
         <v>21</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>632</v>
+        <v>150</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
@@ -35172,19 +35195,19 @@
         <v>21</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH264" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI264" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="AJ264" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK264" t="s" s="2">
         <v>21</v>
@@ -35207,10 +35230,10 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -35221,7 +35244,7 @@
         <v>81</v>
       </c>
       <c r="G265" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H265" t="s" s="2">
         <v>21</v>
@@ -35233,13 +35256,13 @@
         <v>21</v>
       </c>
       <c r="K265" t="s" s="2">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>636</v>
+        <v>136</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>636</v>
+        <v>137</v>
       </c>
       <c r="N265" s="2"/>
       <c r="O265" s="2"/>
@@ -35278,31 +35301,29 @@
         <v>21</v>
       </c>
       <c r="AB265" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC265" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC265" s="2"/>
       <c r="AD265" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE265" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>637</v>
+        <v>162</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH265" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI265" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ265" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK265" t="s" s="2">
         <v>21</v>
@@ -35325,12 +35346,14 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>957</v>
-      </c>
-      <c r="C266" s="2"/>
+        <v>960</v>
+      </c>
+      <c r="C266" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="D266" t="s" s="2">
         <v>21</v>
       </c>
@@ -35351,18 +35374,16 @@
         <v>21</v>
       </c>
       <c r="K266" t="s" s="2">
-        <v>282</v>
+        <v>632</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>958</v>
+        <v>633</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>959</v>
+        <v>634</v>
       </c>
       <c r="N266" s="2"/>
-      <c r="O266" t="s" s="2">
-        <v>960</v>
-      </c>
+      <c r="O266" s="2"/>
       <c r="P266" t="s" s="2">
         <v>21</v>
       </c>
@@ -35410,34 +35431,34 @@
         <v>21</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>957</v>
+        <v>162</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH266" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI266" t="s" s="2">
-        <v>961</v>
+        <v>147</v>
       </c>
       <c r="AJ266" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK266" t="s" s="2">
-        <v>962</v>
+        <v>21</v>
       </c>
       <c r="AL266" t="s" s="2">
-        <v>963</v>
+        <v>21</v>
       </c>
       <c r="AM266" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="AN266" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO266" t="s" s="2">
-        <v>964</v>
+        <v>21</v>
       </c>
       <c r="AP266" t="s" s="2">
         <v>21</v>
@@ -35445,10 +35466,10 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -35471,13 +35492,13 @@
         <v>21</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>966</v>
+        <v>636</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>967</v>
+        <v>636</v>
       </c>
       <c r="N267" s="2"/>
       <c r="O267" s="2"/>
@@ -35528,7 +35549,7 @@
         <v>21</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>965</v>
+        <v>637</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>81</v>
@@ -35540,16 +35561,16 @@
         <v>21</v>
       </c>
       <c r="AJ267" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK267" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="AL267" t="s" s="2">
-        <v>968</v>
+        <v>21</v>
       </c>
       <c r="AM267" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="AN267" t="s" s="2">
         <v>21</v>
@@ -35563,10 +35584,10 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -35577,7 +35598,7 @@
         <v>81</v>
       </c>
       <c r="G268" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H268" t="s" s="2">
         <v>21</v>
@@ -35589,19 +35610,17 @@
         <v>21</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>851</v>
+        <v>282</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>971</v>
-      </c>
-      <c r="N268" t="s" s="2">
-        <v>972</v>
-      </c>
+        <v>965</v>
+      </c>
+      <c r="N268" s="2"/>
       <c r="O268" t="s" s="2">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>21</v>
@@ -35650,34 +35669,34 @@
         <v>21</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH268" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI268" t="s" s="2">
-        <v>21</v>
+        <v>967</v>
       </c>
       <c r="AJ268" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK268" t="s" s="2">
-        <v>21</v>
+        <v>968</v>
       </c>
       <c r="AL268" t="s" s="2">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>975</v>
+        <v>154</v>
       </c>
       <c r="AN268" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO268" t="s" s="2">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AP268" t="s" s="2">
         <v>21</v>
@@ -35685,10 +35704,10 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -35711,13 +35730,13 @@
         <v>21</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>151</v>
+        <v>972</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>152</v>
+        <v>973</v>
       </c>
       <c r="N269" s="2"/>
       <c r="O269" s="2"/>
@@ -35768,7 +35787,7 @@
         <v>21</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>153</v>
+        <v>971</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>81</v>
@@ -35780,16 +35799,16 @@
         <v>21</v>
       </c>
       <c r="AJ269" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK269" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="AL269" t="s" s="2">
+        <v>974</v>
+      </c>
+      <c r="AM269" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AM269" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AN269" t="s" s="2">
         <v>21</v>
@@ -35803,14 +35822,14 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="E270" s="2"/>
       <c r="F270" t="s" s="2">
@@ -35829,18 +35848,20 @@
         <v>21</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>135</v>
+        <v>856</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>158</v>
+        <v>976</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>159</v>
+        <v>977</v>
       </c>
       <c r="N270" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O270" s="2"/>
+        <v>978</v>
+      </c>
+      <c r="O270" t="s" s="2">
+        <v>979</v>
+      </c>
       <c r="P270" t="s" s="2">
         <v>21</v>
       </c>
@@ -35888,7 +35909,7 @@
         <v>21</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>162</v>
+        <v>975</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>81</v>
@@ -35900,16 +35921,16 @@
         <v>21</v>
       </c>
       <c r="AJ270" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK270" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL270" t="s" s="2">
-        <v>154</v>
+        <v>980</v>
       </c>
       <c r="AM270" t="s" s="2">
-        <v>21</v>
+        <v>981</v>
       </c>
       <c r="AN270" t="s" s="2">
         <v>21</v>
@@ -35923,46 +35944,42 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
-        <v>861</v>
+        <v>21</v>
       </c>
       <c r="E271" s="2"/>
       <c r="F271" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G271" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H271" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I271" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J271" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K271" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>862</v>
+        <v>151</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="N271" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O271" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N271" s="2"/>
+      <c r="O271" s="2"/>
       <c r="P271" t="s" s="2">
         <v>21</v>
       </c>
@@ -36010,25 +36027,25 @@
         <v>21</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>864</v>
+        <v>153</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH271" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI271" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ271" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK271" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL271" t="s" s="2">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="AM271" t="s" s="2">
         <v>21</v>
@@ -36045,21 +36062,21 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="E272" s="2"/>
       <c r="F272" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G272" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H272" t="s" s="2">
         <v>21</v>
@@ -36071,20 +36088,18 @@
         <v>21</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>980</v>
+        <v>158</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>981</v>
+        <v>159</v>
       </c>
       <c r="N272" t="s" s="2">
-        <v>982</v>
-      </c>
-      <c r="O272" t="s" s="2">
-        <v>983</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="O272" s="2"/>
       <c r="P272" t="s" s="2">
         <v>21</v>
       </c>
@@ -36108,13 +36123,13 @@
         <v>21</v>
       </c>
       <c r="X272" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="Y272" t="s" s="2">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="Z272" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AA272" t="s" s="2">
         <v>21</v>
@@ -36132,34 +36147,34 @@
         <v>21</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>979</v>
+        <v>162</v>
       </c>
       <c r="AG272" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH272" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI272" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ272" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK272" t="s" s="2">
-        <v>984</v>
+        <v>21</v>
       </c>
       <c r="AL272" t="s" s="2">
-        <v>985</v>
+        <v>154</v>
       </c>
       <c r="AM272" t="s" s="2">
-        <v>986</v>
+        <v>21</v>
       </c>
       <c r="AN272" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO272" t="s" s="2">
-        <v>987</v>
+        <v>21</v>
       </c>
       <c r="AP272" t="s" s="2">
         <v>21</v>
@@ -36167,45 +36182,45 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="E273" s="2"/>
       <c r="F273" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G273" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H273" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I273" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J273" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K273" t="s" s="2">
-        <v>350</v>
+        <v>135</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>989</v>
+        <v>867</v>
       </c>
       <c r="M273" t="s" s="2">
-        <v>990</v>
+        <v>868</v>
       </c>
       <c r="N273" t="s" s="2">
-        <v>991</v>
+        <v>160</v>
       </c>
       <c r="O273" t="s" s="2">
-        <v>992</v>
+        <v>226</v>
       </c>
       <c r="P273" t="s" s="2">
         <v>21</v>
@@ -36254,34 +36269,34 @@
         <v>21</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>988</v>
+        <v>869</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH273" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI273" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ273" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK273" t="s" s="2">
-        <v>993</v>
+        <v>21</v>
       </c>
       <c r="AL273" t="s" s="2">
-        <v>994</v>
+        <v>133</v>
       </c>
       <c r="AM273" t="s" s="2">
-        <v>995</v>
+        <v>21</v>
       </c>
       <c r="AN273" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO273" t="s" s="2">
-        <v>996</v>
+        <v>21</v>
       </c>
       <c r="AP273" t="s" s="2">
         <v>21</v>
@@ -36289,21 +36304,21 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>997</v>
+        <v>985</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>997</v>
+        <v>985</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
-        <v>998</v>
+        <v>21</v>
       </c>
       <c r="E274" s="2"/>
       <c r="F274" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G274" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H274" t="s" s="2">
         <v>21</v>
@@ -36315,18 +36330,20 @@
         <v>21</v>
       </c>
       <c r="K274" t="s" s="2">
-        <v>999</v>
+        <v>179</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>1000</v>
+        <v>986</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>1001</v>
+        <v>987</v>
       </c>
       <c r="N274" t="s" s="2">
-        <v>1002</v>
-      </c>
-      <c r="O274" s="2"/>
+        <v>988</v>
+      </c>
+      <c r="O274" t="s" s="2">
+        <v>989</v>
+      </c>
       <c r="P274" t="s" s="2">
         <v>21</v>
       </c>
@@ -36350,13 +36367,13 @@
         <v>21</v>
       </c>
       <c r="X274" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="Y274" t="s" s="2">
-        <v>21</v>
+        <v>115</v>
       </c>
       <c r="Z274" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="AA274" t="s" s="2">
         <v>21</v>
@@ -36374,13 +36391,13 @@
         <v>21</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>997</v>
+        <v>985</v>
       </c>
       <c r="AG274" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AH274" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI274" t="s" s="2">
         <v>21</v>
@@ -36389,19 +36406,19 @@
         <v>102</v>
       </c>
       <c r="AK274" t="s" s="2">
-        <v>1003</v>
+        <v>990</v>
       </c>
       <c r="AL274" t="s" s="2">
-        <v>1004</v>
+        <v>991</v>
       </c>
       <c r="AM274" t="s" s="2">
-        <v>154</v>
+        <v>992</v>
       </c>
       <c r="AN274" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO274" t="s" s="2">
-        <v>1005</v>
+        <v>993</v>
       </c>
       <c r="AP274" t="s" s="2">
         <v>21</v>
@@ -36409,10 +36426,10 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>1006</v>
+        <v>994</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>1006</v>
+        <v>994</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -36432,22 +36449,22 @@
         <v>21</v>
       </c>
       <c r="J275" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K275" t="s" s="2">
-        <v>282</v>
+        <v>350</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>1008</v>
+        <v>996</v>
       </c>
       <c r="N275" t="s" s="2">
-        <v>1009</v>
+        <v>997</v>
       </c>
       <c r="O275" t="s" s="2">
-        <v>1010</v>
+        <v>998</v>
       </c>
       <c r="P275" t="s" s="2">
         <v>21</v>
@@ -36496,7 +36513,7 @@
         <v>21</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>1006</v>
+        <v>994</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>81</v>
@@ -36511,19 +36528,19 @@
         <v>102</v>
       </c>
       <c r="AK275" t="s" s="2">
-        <v>1011</v>
+        <v>999</v>
       </c>
       <c r="AL275" t="s" s="2">
-        <v>963</v>
+        <v>1000</v>
       </c>
       <c r="AM275" t="s" s="2">
-        <v>1012</v>
+        <v>1001</v>
       </c>
       <c r="AN275" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO275" t="s" s="2">
-        <v>21</v>
+        <v>1002</v>
       </c>
       <c r="AP275" t="s" s="2">
         <v>21</v>
@@ -36531,14 +36548,14 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>1013</v>
+        <v>1003</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>1013</v>
+        <v>1003</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
-        <v>21</v>
+        <v>1004</v>
       </c>
       <c r="E276" s="2"/>
       <c r="F276" t="s" s="2">
@@ -36551,26 +36568,24 @@
         <v>21</v>
       </c>
       <c r="I276" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J276" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K276" t="s" s="2">
-        <v>851</v>
+        <v>1005</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="N276" t="s" s="2">
-        <v>1016</v>
-      </c>
-      <c r="O276" t="s" s="2">
-        <v>1017</v>
-      </c>
+        <v>1008</v>
+      </c>
+      <c r="O276" s="2"/>
       <c r="P276" t="s" s="2">
         <v>21</v>
       </c>
@@ -36618,7 +36633,7 @@
         <v>21</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>1013</v>
+        <v>1003</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>81</v>
@@ -36633,10 +36648,10 @@
         <v>102</v>
       </c>
       <c r="AK276" t="s" s="2">
-        <v>21</v>
+        <v>1009</v>
       </c>
       <c r="AL276" t="s" s="2">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="AM276" t="s" s="2">
         <v>154</v>
@@ -36645,7 +36660,7 @@
         <v>21</v>
       </c>
       <c r="AO276" t="s" s="2">
-        <v>21</v>
+        <v>1011</v>
       </c>
       <c r="AP276" t="s" s="2">
         <v>21</v>
@@ -36653,10 +36668,10 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -36676,19 +36691,23 @@
         <v>21</v>
       </c>
       <c r="J277" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>150</v>
+        <v>282</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>151</v>
+        <v>1013</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N277" s="2"/>
-      <c r="O277" s="2"/>
+        <v>1014</v>
+      </c>
+      <c r="N277" t="s" s="2">
+        <v>1015</v>
+      </c>
+      <c r="O277" t="s" s="2">
+        <v>1016</v>
+      </c>
       <c r="P277" t="s" s="2">
         <v>21</v>
       </c>
@@ -36736,7 +36755,7 @@
         <v>21</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>153</v>
+        <v>1012</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>81</v>
@@ -36748,16 +36767,16 @@
         <v>21</v>
       </c>
       <c r="AJ277" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK277" t="s" s="2">
-        <v>21</v>
+        <v>1017</v>
       </c>
       <c r="AL277" t="s" s="2">
-        <v>154</v>
+        <v>969</v>
       </c>
       <c r="AM277" t="s" s="2">
-        <v>21</v>
+        <v>1018</v>
       </c>
       <c r="AN277" t="s" s="2">
         <v>21</v>
@@ -36771,14 +36790,14 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="E278" s="2"/>
       <c r="F278" t="s" s="2">
@@ -36791,24 +36810,26 @@
         <v>21</v>
       </c>
       <c r="I278" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J278" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K278" t="s" s="2">
-        <v>135</v>
+        <v>856</v>
       </c>
       <c r="L278" t="s" s="2">
-        <v>158</v>
+        <v>1020</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>159</v>
+        <v>1021</v>
       </c>
       <c r="N278" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O278" s="2"/>
+        <v>1022</v>
+      </c>
+      <c r="O278" t="s" s="2">
+        <v>1023</v>
+      </c>
       <c r="P278" t="s" s="2">
         <v>21</v>
       </c>
@@ -36856,7 +36877,7 @@
         <v>21</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>162</v>
+        <v>1019</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>81</v>
@@ -36868,16 +36889,16 @@
         <v>21</v>
       </c>
       <c r="AJ278" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK278" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL278" t="s" s="2">
+        <v>1024</v>
+      </c>
+      <c r="AM278" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AM278" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AN278" t="s" s="2">
         <v>21</v>
@@ -36891,46 +36912,42 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
-        <v>861</v>
+        <v>21</v>
       </c>
       <c r="E279" s="2"/>
       <c r="F279" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G279" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H279" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I279" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J279" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>862</v>
+        <v>151</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="N279" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O279" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N279" s="2"/>
+      <c r="O279" s="2"/>
       <c r="P279" t="s" s="2">
         <v>21</v>
       </c>
@@ -36978,25 +36995,25 @@
         <v>21</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>864</v>
+        <v>153</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH279" t="s" s="2">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="AI279" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ279" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK279" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL279" t="s" s="2">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="AM279" t="s" s="2">
         <v>21</v>
@@ -37013,21 +37030,21 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="E280" s="2"/>
       <c r="F280" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G280" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H280" t="s" s="2">
         <v>21</v>
@@ -37036,19 +37053,19 @@
         <v>21</v>
       </c>
       <c r="J280" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>1023</v>
+        <v>135</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>1024</v>
+        <v>158</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>1025</v>
+        <v>159</v>
       </c>
       <c r="N280" t="s" s="2">
-        <v>1026</v>
+        <v>160</v>
       </c>
       <c r="O280" s="2"/>
       <c r="P280" t="s" s="2">
@@ -37098,34 +37115,34 @@
         <v>21</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>1022</v>
+        <v>162</v>
       </c>
       <c r="AG280" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AH280" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="AI280" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ280" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK280" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL280" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AL280" t="s" s="2">
-        <v>234</v>
-      </c>
       <c r="AM280" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="AN280" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO280" t="s" s="2">
-        <v>1027</v>
+        <v>21</v>
       </c>
       <c r="AP280" t="s" s="2">
         <v>21</v>
@@ -37133,42 +37150,46 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="E281" s="2"/>
       <c r="F281" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G281" t="s" s="2">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H281" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I281" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J281" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>1029</v>
+        <v>867</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>1030</v>
-      </c>
-      <c r="N281" s="2"/>
-      <c r="O281" s="2"/>
+        <v>868</v>
+      </c>
+      <c r="N281" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O281" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P281" t="s" s="2">
         <v>21</v>
       </c>
@@ -37192,60 +37213,298 @@
         <v>21</v>
       </c>
       <c r="X281" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y281" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z281" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA281" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB281" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC281" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD281" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE281" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF281" t="s" s="2">
+        <v>869</v>
+      </c>
+      <c r="AG281" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH281" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI281" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ281" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK281" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL281" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AM281" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN281" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO281" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP281" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="2">
+        <v>1028</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>1028</v>
+      </c>
+      <c r="C282" s="2"/>
+      <c r="D282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E282" s="2"/>
+      <c r="F282" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G282" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J282" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K282" t="s" s="2">
+        <v>1029</v>
+      </c>
+      <c r="L282" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="M282" t="s" s="2">
+        <v>1031</v>
+      </c>
+      <c r="N282" t="s" s="2">
+        <v>1032</v>
+      </c>
+      <c r="O282" s="2"/>
+      <c r="P282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q282" s="2"/>
+      <c r="R282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF282" t="s" s="2">
+        <v>1028</v>
+      </c>
+      <c r="AG282" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH282" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ282" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK282" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AL282" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AM282" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AN282" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO282" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="AP282" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="2">
+        <v>1034</v>
+      </c>
+      <c r="B283" t="s" s="2">
+        <v>1034</v>
+      </c>
+      <c r="C283" s="2"/>
+      <c r="D283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E283" s="2"/>
+      <c r="F283" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G283" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J283" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K283" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L283" t="s" s="2">
+        <v>1035</v>
+      </c>
+      <c r="M283" t="s" s="2">
+        <v>1036</v>
+      </c>
+      <c r="N283" s="2"/>
+      <c r="O283" s="2"/>
+      <c r="P283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q283" s="2"/>
+      <c r="R283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X283" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="Y281" t="s" s="2">
-        <v>1030</v>
-      </c>
-      <c r="Z281" t="s" s="2">
-        <v>1031</v>
-      </c>
-      <c r="AA281" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB281" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC281" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD281" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE281" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF281" t="s" s="2">
-        <v>1028</v>
-      </c>
-      <c r="AG281" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH281" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI281" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ281" t="s" s="2">
+      <c r="Y283" t="s" s="2">
+        <v>1036</v>
+      </c>
+      <c r="Z283" t="s" s="2">
+        <v>1037</v>
+      </c>
+      <c r="AA283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF283" t="s" s="2">
+        <v>1034</v>
+      </c>
+      <c r="AG283" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH283" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ283" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK281" t="s" s="2">
+      <c r="AK283" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AL281" t="s" s="2">
-        <v>1032</v>
-      </c>
-      <c r="AM281" t="s" s="2">
+      <c r="AL283" t="s" s="2">
+        <v>1038</v>
+      </c>
+      <c r="AM283" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AN281" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO281" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AP281" t="s" s="2">
+      <c r="AN283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO283" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AP283" t="s" s="2">
         <v>21</v>
       </c>
     </row>
